--- a/HSI_FSC_result/4. C Way/score_5way.xlsx
+++ b/HSI_FSC_result/4. C Way/score_5way.xlsx
@@ -5,17 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Document\DevelopProject\Develop_DeepLearning\HSI\HSI-FSC\HSI_FSC_4_5way\result\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Document\DevelopProject\Develop_DeepLearning\HSI\HSI-FSC\HSI_FSC_result\4. C Way\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{004B5275-5A40-4572-9EBF-1CA7C0E92C15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AADF86FB-0C44-4CEF-87C5-56EFDF2EAF5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7950" yWindow="1605" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="360" yWindow="2940" windowWidth="21600" windowHeight="12885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IP" sheetId="1" r:id="rId1"/>
-    <sheet name="SA" sheetId="2" r:id="rId2"/>
-    <sheet name="UP" sheetId="3" r:id="rId3"/>
+    <sheet name="UP" sheetId="3" r:id="rId2"/>
+    <sheet name="SA" sheetId="2" r:id="rId3"/>
     <sheet name="XZ" sheetId="5" r:id="rId4"/>
     <sheet name="PC" sheetId="4" r:id="rId5"/>
   </sheets>
@@ -39,12 +39,19 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -79,7 +86,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -358,9 +365,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1">
         <v>18.442623000000001</v>
       </c>
@@ -396,7 +403,7 @@
         <v>41.32879539999999</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>50.952379999999998</v>
       </c>
@@ -432,7 +439,7 @@
         <v>55.715583599999988</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>70.032570000000007</v>
       </c>
@@ -468,7 +475,7 @@
         <v>44.282788600000003</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>34.645670000000003</v>
       </c>
@@ -504,7 +511,7 @@
         <v>39.710917000000002</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>91.150443999999993</v>
       </c>
@@ -540,7 +547,7 @@
         <v>69.118913699999993</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>73.134320000000002</v>
       </c>
@@ -576,7 +583,7 @@
         <v>82.180721299999988</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>43.75</v>
       </c>
@@ -612,7 +619,7 @@
         <v>38.386761899999996</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>83.849556000000007</v>
       </c>
@@ -648,7 +655,7 @@
         <v>90.027924600000006</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>25.974025999999999</v>
       </c>
@@ -684,7 +691,7 @@
         <v>20.348855700000001</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>32.970027999999999</v>
       </c>
@@ -720,7 +727,7 @@
         <v>37.701961099999998</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>44.615383000000001</v>
       </c>
@@ -756,7 +763,7 @@
         <v>64.01695629999999</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>40.893065999999997</v>
       </c>
@@ -792,7 +799,7 @@
         <v>42.456569299999998</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>78.764480000000006</v>
       </c>
@@ -828,7 +835,7 @@
         <v>67.68494530000001</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>93.861069999999998</v>
       </c>
@@ -864,7 +871,7 @@
         <v>92.663549000000017</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>75.920680000000004</v>
       </c>
@@ -900,7 +907,7 @@
         <v>52.552967000000002</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>43.867924000000002</v>
       </c>
@@ -936,7 +943,7 @@
         <v>60.474439699999991</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>56.259147233876398</v>
       </c>
@@ -972,7 +979,7 @@
         <v>57.510976680651709</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>56.426513195037799</v>
       </c>
@@ -1008,7 +1015,7 @@
         <v>56.165791153907719</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>51.636231332121099</v>
       </c>
@@ -1045,1153 +1052,1146 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10C6D9CA-287C-4A13-BF9B-099121023619}">
-  <dimension ref="A1:K19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BF268C6-262B-4B5D-895F-55B8B1A5BC12}">
+  <dimension ref="A1:K12"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1">
-        <v>68.122489999999999</v>
+        <v>93.235889999999998</v>
       </c>
       <c r="B1">
-        <v>82.640884</v>
+        <v>94.462135000000004</v>
       </c>
       <c r="C1">
-        <v>94.719470000000001</v>
+        <v>93.206860000000006</v>
       </c>
       <c r="D1">
-        <v>70.68965</v>
+        <v>85.093795999999998</v>
       </c>
       <c r="E1">
-        <v>96.816209999999998</v>
+        <v>92.653149999999997</v>
       </c>
       <c r="F1">
-        <v>81.303460000000001</v>
+        <v>89.960909999999998</v>
       </c>
       <c r="G1">
-        <v>100</v>
+        <v>95.566055000000006</v>
       </c>
       <c r="H1">
-        <v>99.503720000000001</v>
+        <v>89.208070000000006</v>
       </c>
       <c r="I1">
-        <v>85.78407</v>
+        <v>72.08681</v>
       </c>
       <c r="J1">
-        <v>89.639435000000006</v>
+        <v>94.484979999999993</v>
       </c>
       <c r="K1" s="1">
-        <f>AVERAGE(A1:J1)</f>
-        <v>86.921938900000015</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+        <v>89.995865600000002</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2">
-        <v>81.649870000000007</v>
+        <v>88.884699999999995</v>
       </c>
       <c r="B2">
-        <v>97.291790000000006</v>
+        <v>98.463806000000005</v>
       </c>
       <c r="C2">
-        <v>96.923900000000003</v>
+        <v>97.545044000000004</v>
       </c>
       <c r="D2">
-        <v>99.915139999999994</v>
+        <v>93.906234999999995</v>
       </c>
       <c r="E2">
-        <v>90.509150000000005</v>
+        <v>90.560103999999995</v>
       </c>
       <c r="F2">
-        <v>96.4876</v>
+        <v>89.533905000000004</v>
       </c>
       <c r="G2">
-        <v>89.262550000000005</v>
+        <v>92.539670000000001</v>
       </c>
       <c r="H2">
-        <v>99.597854999999996</v>
+        <v>83.149709999999999</v>
       </c>
       <c r="I2">
-        <v>86.408029999999997</v>
+        <v>97.874129999999994</v>
       </c>
       <c r="J2">
-        <v>96.127809999999997</v>
+        <v>97.836820000000003</v>
       </c>
       <c r="K2" s="1">
-        <f t="shared" ref="K2:K19" si="0">AVERAGE(A2:J2)</f>
-        <v>93.417369499999992</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+        <v>93.029412399999998</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3">
-        <v>98.099045000000004</v>
+        <v>64.91713</v>
       </c>
       <c r="B3">
-        <v>100</v>
+        <v>58.694830000000003</v>
       </c>
       <c r="C3">
-        <v>74.857795999999993</v>
+        <v>53.138236999999997</v>
       </c>
       <c r="D3">
-        <v>98.436713999999995</v>
+        <v>81.394159999999999</v>
       </c>
       <c r="E3">
-        <v>60.684615999999998</v>
+        <v>34.964302000000004</v>
       </c>
       <c r="F3">
-        <v>88.159255999999999</v>
+        <v>81.120149999999995</v>
       </c>
       <c r="G3">
-        <v>79.897999999999996</v>
+        <v>73.232085999999995</v>
       </c>
       <c r="H3">
-        <v>95.682379999999995</v>
+        <v>41.018925000000003</v>
       </c>
       <c r="I3">
-        <v>85.65719</v>
+        <v>39.097285999999997</v>
       </c>
       <c r="J3">
-        <v>98.268839999999997</v>
+        <v>38.339134000000001</v>
       </c>
       <c r="K3" s="1">
-        <f t="shared" si="0"/>
-        <v>87.974383700000004</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+        <v>56.591624000000003</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4">
-        <v>91.760050000000007</v>
+        <v>82.764560000000003</v>
       </c>
       <c r="B4">
-        <v>81.883194000000003</v>
+        <v>90.35727</v>
       </c>
       <c r="C4">
-        <v>75.33802</v>
+        <v>70.561859999999996</v>
       </c>
       <c r="D4">
-        <v>75.432900000000004</v>
+        <v>66.633960000000002</v>
       </c>
       <c r="E4">
-        <v>92.94829</v>
+        <v>93.272670000000005</v>
       </c>
       <c r="F4">
-        <v>94.474760000000003</v>
+        <v>87.862520000000004</v>
       </c>
       <c r="G4">
-        <v>98.429694999999995</v>
+        <v>84.869</v>
       </c>
       <c r="H4">
-        <v>91.08614</v>
+        <v>37.139656000000002</v>
       </c>
       <c r="I4">
-        <v>85.732010000000002</v>
+        <v>82.696820000000002</v>
       </c>
       <c r="J4">
-        <v>88.436689999999999</v>
+        <v>89.617660000000001</v>
       </c>
       <c r="K4" s="1">
-        <f t="shared" si="0"/>
-        <v>87.552174899999997</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+        <v>78.577597600000004</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5">
-        <v>99.318436000000005</v>
+        <v>96.881799999999998</v>
       </c>
       <c r="B5">
-        <v>93.599159999999998</v>
+        <v>94.585089999999994</v>
       </c>
       <c r="C5">
-        <v>99.508895999999993</v>
+        <v>98.383539999999996</v>
       </c>
       <c r="D5">
-        <v>99.064229999999995</v>
+        <v>95.187545999999998</v>
       </c>
       <c r="E5">
-        <v>95.591179999999994</v>
+        <v>99.554564999999997</v>
       </c>
       <c r="F5">
-        <v>88.502210000000005</v>
+        <v>85.997444000000002</v>
       </c>
       <c r="G5">
-        <v>97.16507</v>
+        <v>86.05247</v>
       </c>
       <c r="H5">
-        <v>92.777780000000007</v>
+        <v>94.651650000000004</v>
       </c>
       <c r="I5">
-        <v>97.767685</v>
+        <v>93.723259999999996</v>
       </c>
       <c r="J5">
-        <v>97.410285999999999</v>
+        <v>97.777780000000007</v>
       </c>
       <c r="K5" s="1">
-        <f t="shared" si="0"/>
-        <v>96.07049330000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+        <v>94.279514500000005</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6">
-        <v>99.797470000000004</v>
+        <v>39.682755</v>
       </c>
       <c r="B6">
-        <v>92.269149999999996</v>
+        <v>39.441699999999997</v>
       </c>
       <c r="C6">
-        <v>96.726119999999995</v>
+        <v>44.923960000000001</v>
       </c>
       <c r="D6">
-        <v>100</v>
+        <v>36.876710000000003</v>
       </c>
       <c r="E6">
-        <v>99.049285999999995</v>
+        <v>38.666812999999998</v>
       </c>
       <c r="F6">
-        <v>100</v>
+        <v>57.435524000000001</v>
       </c>
       <c r="G6">
-        <v>100</v>
+        <v>58.438366000000002</v>
       </c>
       <c r="H6">
-        <v>100</v>
+        <v>32.903399999999998</v>
       </c>
       <c r="I6">
-        <v>98.656679999999994</v>
+        <v>61.194262999999999</v>
       </c>
       <c r="J6">
-        <v>99.793390000000002</v>
+        <v>48.840220000000002</v>
       </c>
       <c r="K6" s="1">
-        <f t="shared" si="0"/>
-        <v>98.62920960000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+        <v>45.840371099999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7">
-        <v>93.83887</v>
+        <v>58.860152999999997</v>
       </c>
       <c r="B7">
-        <v>98.471739999999997</v>
+        <v>59.706963000000002</v>
       </c>
       <c r="C7">
-        <v>97.036569999999998</v>
+        <v>77.061676000000006</v>
       </c>
       <c r="D7">
-        <v>94.211579999999998</v>
+        <v>67.0685</v>
       </c>
       <c r="E7">
-        <v>97.669200000000004</v>
+        <v>67.460750000000004</v>
       </c>
       <c r="F7">
-        <v>86.02852</v>
+        <v>70.969695999999999</v>
       </c>
       <c r="G7">
-        <v>100</v>
+        <v>56.861060000000002</v>
       </c>
       <c r="H7">
-        <v>94.619315999999998</v>
+        <v>46.754677000000001</v>
       </c>
       <c r="I7">
-        <v>89.819694999999996</v>
+        <v>40.609473999999999</v>
       </c>
       <c r="J7">
-        <v>94.869730000000004</v>
+        <v>60.408366999999998</v>
       </c>
       <c r="K7" s="1">
-        <f t="shared" si="0"/>
-        <v>94.656522100000004</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+        <v>60.576131599999997</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8">
-        <v>80.543499999999995</v>
+        <v>77.40616</v>
       </c>
       <c r="B8">
-        <v>93.096050000000005</v>
+        <v>74.783379999999994</v>
       </c>
       <c r="C8">
-        <v>81.272480000000002</v>
+        <v>72.513724999999994</v>
       </c>
       <c r="D8">
-        <v>81.703370000000007</v>
+        <v>84.737624999999994</v>
       </c>
       <c r="E8">
-        <v>89.491164999999995</v>
+        <v>65.450860000000006</v>
       </c>
       <c r="F8">
-        <v>88.131270000000001</v>
+        <v>71.288709999999995</v>
       </c>
       <c r="G8">
-        <v>76.253649999999993</v>
+        <v>85.139595</v>
       </c>
       <c r="H8">
-        <v>98.103520000000003</v>
+        <v>78.072069999999997</v>
       </c>
       <c r="I8">
-        <v>88.588920000000002</v>
+        <v>67.378270000000001</v>
       </c>
       <c r="J8">
-        <v>86.7102</v>
+        <v>76.251080000000002</v>
       </c>
       <c r="K8" s="1">
-        <f t="shared" si="0"/>
-        <v>86.389412500000006</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+        <v>75.302147500000004</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9">
-        <v>98.443950000000001</v>
+        <v>88.015339999999995</v>
       </c>
       <c r="B9">
-        <v>99.037480000000002</v>
+        <v>87.931039999999996</v>
       </c>
       <c r="C9">
-        <v>99.897720000000007</v>
+        <v>86.514719999999997</v>
       </c>
       <c r="D9">
-        <v>99.864620000000002</v>
+        <v>98.26464</v>
       </c>
       <c r="E9">
-        <v>95.889983999999998</v>
+        <v>97.848240000000004</v>
       </c>
       <c r="F9">
-        <v>99.929839999999999</v>
+        <v>81.363640000000004</v>
       </c>
       <c r="G9">
-        <v>97.776349999999994</v>
+        <v>75.729163999999997</v>
       </c>
       <c r="H9">
-        <v>98.736046000000002</v>
+        <v>63.87697</v>
       </c>
       <c r="I9">
-        <v>98.536270000000002</v>
+        <v>77.985740000000007</v>
       </c>
       <c r="J9">
-        <v>84.487465</v>
+        <v>75.922809999999998</v>
       </c>
       <c r="K9" s="1">
-        <f t="shared" si="0"/>
-        <v>97.259972499999989</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+        <v>83.345230400000005</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10">
-        <v>99.681219999999996</v>
+        <v>77.344772769777407</v>
       </c>
       <c r="B10">
-        <v>98.865036000000003</v>
+        <v>75.797175986534498</v>
       </c>
       <c r="C10">
-        <v>87.969480000000004</v>
+        <v>76.323171872077793</v>
       </c>
       <c r="D10">
-        <v>97.40061</v>
+        <v>72.105853749766197</v>
       </c>
       <c r="E10">
-        <v>98.292090000000002</v>
+        <v>71.247896016457801</v>
       </c>
       <c r="F10">
-        <v>94.473579999999998</v>
+        <v>82.020291752384495</v>
       </c>
       <c r="G10">
-        <v>92.245369999999994</v>
+        <v>83.046568169066703</v>
       </c>
       <c r="H10">
-        <v>99.386690000000002</v>
+        <v>62.083878810547901</v>
       </c>
       <c r="I10">
-        <v>99.533259999999999</v>
+        <v>76.447073125116802</v>
       </c>
       <c r="J10">
-        <v>91.210380000000001</v>
+        <v>77.417243314007806</v>
       </c>
       <c r="K10" s="1">
-        <f t="shared" si="0"/>
-        <v>95.905771600000008</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+        <v>75.383392560000004</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11">
-        <v>100</v>
+        <v>76.738715171813894</v>
       </c>
       <c r="B11">
-        <v>98.290595999999994</v>
+        <v>77.602916955947805</v>
       </c>
       <c r="C11">
-        <v>94.303799999999995</v>
+        <v>77.094399929046602</v>
       </c>
       <c r="D11">
-        <v>65.382225000000005</v>
+        <v>78.795903921127305</v>
       </c>
       <c r="E11">
-        <v>92.781689999999998</v>
+        <v>75.603497028350802</v>
       </c>
       <c r="F11">
-        <v>77.097009999999997</v>
+        <v>79.503607749938894</v>
       </c>
       <c r="G11">
-        <v>91.913049999999998</v>
+        <v>78.714162111282306</v>
       </c>
       <c r="H11">
-        <v>84.963620000000006</v>
+        <v>62.975013256072998</v>
       </c>
       <c r="I11">
-        <v>82.211913999999993</v>
+        <v>70.294010639190603</v>
       </c>
       <c r="J11">
-        <v>98.886830000000003</v>
+        <v>75.497651100158606</v>
       </c>
       <c r="K11" s="1">
-        <f t="shared" si="0"/>
-        <v>88.583073499999983</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+        <v>75.281987790000002</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12">
-        <v>99.424385000000001</v>
+        <v>70.852684532399905</v>
       </c>
       <c r="B12">
-        <v>97.704089999999994</v>
+        <v>69.970656371112895</v>
       </c>
       <c r="C12">
-        <v>99.737260000000006</v>
+        <v>70.499030292927301</v>
       </c>
       <c r="D12">
-        <v>100</v>
+        <v>65.595863087811097</v>
       </c>
       <c r="E12">
-        <v>85.044250000000005</v>
+        <v>63.774972074662998</v>
       </c>
       <c r="F12">
-        <v>100</v>
+        <v>76.354593179033898</v>
       </c>
       <c r="G12">
-        <v>95.868589999999998</v>
+        <v>77.981995391157298</v>
       </c>
       <c r="H12">
-        <v>99.058080000000004</v>
+        <v>53.582865881859497</v>
       </c>
       <c r="I12">
-        <v>100</v>
+        <v>69.969290706866303</v>
       </c>
       <c r="J12">
-        <v>99.896050000000002</v>
+        <v>71.530112392570899</v>
       </c>
       <c r="K12" s="1">
-        <f t="shared" si="0"/>
-        <v>97.673270500000015</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>99.563800000000001</v>
-      </c>
-      <c r="B13">
-        <v>98.494630000000001</v>
-      </c>
-      <c r="C13">
-        <v>97.337590000000006</v>
-      </c>
-      <c r="D13">
-        <v>87.404579999999996</v>
-      </c>
-      <c r="E13">
-        <v>97.749200000000002</v>
-      </c>
-      <c r="F13">
-        <v>91.497979999999998</v>
-      </c>
-      <c r="G13">
-        <v>96.805115000000001</v>
-      </c>
-      <c r="H13">
-        <v>99.890945000000002</v>
-      </c>
-      <c r="I13">
-        <v>87.19453</v>
-      </c>
-      <c r="J13">
-        <v>99.647480000000002</v>
-      </c>
-      <c r="K13" s="1">
-        <f t="shared" si="0"/>
-        <v>95.558584999999994</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>86.743039999999993</v>
-      </c>
-      <c r="B14">
-        <v>95.174260000000004</v>
-      </c>
-      <c r="C14">
-        <v>69.089714000000001</v>
-      </c>
-      <c r="D14">
-        <v>91.650670000000005</v>
-      </c>
-      <c r="E14">
-        <v>88.385993999999997</v>
-      </c>
-      <c r="F14">
-        <v>51.392890000000001</v>
-      </c>
-      <c r="G14">
-        <v>77.463710000000006</v>
-      </c>
-      <c r="H14">
-        <v>98.41713</v>
-      </c>
-      <c r="I14">
-        <v>63.242280000000001</v>
-      </c>
-      <c r="J14">
-        <v>77.242890000000003</v>
-      </c>
-      <c r="K14" s="1">
-        <f t="shared" si="0"/>
-        <v>79.88025780000001</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>72.63964</v>
-      </c>
-      <c r="B15">
-        <v>68.607370000000003</v>
-      </c>
-      <c r="C15">
-        <v>71.331764000000007</v>
-      </c>
-      <c r="D15">
-        <v>65.450355999999999</v>
-      </c>
-      <c r="E15">
-        <v>61.176913999999996</v>
-      </c>
-      <c r="F15">
-        <v>54.978349999999999</v>
-      </c>
-      <c r="G15">
-        <v>64.059970000000007</v>
-      </c>
-      <c r="H15">
-        <v>63.287210000000002</v>
-      </c>
-      <c r="I15">
-        <v>81.664824999999993</v>
-      </c>
-      <c r="J15">
-        <v>74.836020000000005</v>
-      </c>
-      <c r="K15" s="1">
-        <f t="shared" si="0"/>
-        <v>67.803241899999989</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>100</v>
-      </c>
-      <c r="B16">
-        <v>49.952759999999998</v>
-      </c>
-      <c r="C16">
-        <v>72.08081</v>
-      </c>
-      <c r="D16">
-        <v>86.66301</v>
-      </c>
-      <c r="E16">
-        <v>94.965810000000005</v>
-      </c>
-      <c r="F16">
-        <v>90.846050000000005</v>
-      </c>
-      <c r="G16">
-        <v>93.845344999999995</v>
-      </c>
-      <c r="H16">
-        <v>89.5</v>
-      </c>
-      <c r="I16">
-        <v>78.672989999999999</v>
-      </c>
-      <c r="J16">
-        <v>93.087249999999997</v>
-      </c>
-      <c r="K16" s="1">
-        <f t="shared" si="0"/>
-        <v>84.961402499999991</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>88.647490254761706</v>
-      </c>
-      <c r="B17">
-        <v>87.8808032662713</v>
-      </c>
-      <c r="C17">
-        <v>86.639324576474706</v>
-      </c>
-      <c r="D17">
-        <v>86.585748859206703</v>
-      </c>
-      <c r="E17">
-        <v>85.621385948382496</v>
-      </c>
-      <c r="F17">
-        <v>82.384673649984293</v>
-      </c>
-      <c r="G17">
-        <v>86.672578469951404</v>
-      </c>
-      <c r="H17">
-        <v>89.988730624988406</v>
-      </c>
-      <c r="I17">
-        <v>89.135214025753299</v>
-      </c>
-      <c r="J17">
-        <v>88.835928984462996</v>
-      </c>
-      <c r="K17" s="1">
-        <f t="shared" si="0"/>
-        <v>87.239187866023727</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>91.851609945297199</v>
-      </c>
-      <c r="B18">
-        <v>90.336132049560504</v>
-      </c>
-      <c r="C18">
-        <v>88.008213043212805</v>
-      </c>
-      <c r="D18">
-        <v>88.329350948333698</v>
-      </c>
-      <c r="E18">
-        <v>89.815318584442096</v>
-      </c>
-      <c r="F18">
-        <v>86.456423997879</v>
-      </c>
-      <c r="G18">
-        <v>90.686655044555593</v>
-      </c>
-      <c r="H18">
-        <v>94.038152694702106</v>
-      </c>
-      <c r="I18">
-        <v>88.091897964477496</v>
-      </c>
-      <c r="J18">
-        <v>91.909420490264793</v>
-      </c>
-      <c r="K18" s="1">
-        <f t="shared" si="0"/>
-        <v>89.952317476272526</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>87.3622692078971</v>
-      </c>
-      <c r="B19">
-        <v>86.626402722459503</v>
-      </c>
-      <c r="C19">
-        <v>85.177477955344699</v>
-      </c>
-      <c r="D19">
-        <v>85.141995010530593</v>
-      </c>
-      <c r="E19">
-        <v>84.095766866740504</v>
-      </c>
-      <c r="F19">
-        <v>80.582646055009306</v>
-      </c>
-      <c r="G19">
-        <v>85.190171299562707</v>
-      </c>
-      <c r="H19">
-        <v>88.931814027006197</v>
-      </c>
-      <c r="I19">
-        <v>87.932867444048398</v>
-      </c>
-      <c r="J19">
-        <v>87.596572229939596</v>
-      </c>
-      <c r="K19" s="1">
-        <f t="shared" si="0"/>
-        <v>85.863798281853875</v>
+        <v>69.011206389999998</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BF268C6-262B-4B5D-895F-55B8B1A5BC12}">
-  <dimension ref="A1:K12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10C6D9CA-287C-4A13-BF9B-099121023619}">
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1">
-        <v>93.235889999999998</v>
+        <v>68.122489999999999</v>
       </c>
       <c r="B1">
-        <v>94.462135000000004</v>
+        <v>82.640884</v>
       </c>
       <c r="C1">
-        <v>93.206860000000006</v>
+        <v>94.719470000000001</v>
       </c>
       <c r="D1">
-        <v>85.093795999999998</v>
+        <v>70.68965</v>
       </c>
       <c r="E1">
-        <v>92.653149999999997</v>
+        <v>96.816209999999998</v>
       </c>
       <c r="F1">
-        <v>89.960909999999998</v>
+        <v>81.303460000000001</v>
       </c>
       <c r="G1">
-        <v>95.566055000000006</v>
+        <v>100</v>
       </c>
       <c r="H1">
-        <v>89.208070000000006</v>
+        <v>99.503720000000001</v>
       </c>
       <c r="I1">
-        <v>72.08681</v>
+        <v>85.78407</v>
       </c>
       <c r="J1">
-        <v>94.484979999999993</v>
+        <v>89.639435000000006</v>
       </c>
       <c r="K1" s="1">
         <f>AVERAGE(A1:J1)</f>
-        <v>89.995865600000002</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+        <v>86.921938900000015</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2">
-        <v>88.884699999999995</v>
+        <v>81.649870000000007</v>
       </c>
       <c r="B2">
-        <v>98.463806000000005</v>
+        <v>97.291790000000006</v>
       </c>
       <c r="C2">
-        <v>97.545044000000004</v>
+        <v>96.923900000000003</v>
       </c>
       <c r="D2">
-        <v>93.906234999999995</v>
+        <v>99.915139999999994</v>
       </c>
       <c r="E2">
-        <v>90.560103999999995</v>
+        <v>90.509150000000005</v>
       </c>
       <c r="F2">
-        <v>89.533905000000004</v>
+        <v>96.4876</v>
       </c>
       <c r="G2">
-        <v>92.539670000000001</v>
+        <v>89.262550000000005</v>
       </c>
       <c r="H2">
-        <v>83.149709999999999</v>
+        <v>99.597854999999996</v>
       </c>
       <c r="I2">
-        <v>97.874129999999994</v>
+        <v>86.408029999999997</v>
       </c>
       <c r="J2">
-        <v>97.836820000000003</v>
+        <v>96.127809999999997</v>
       </c>
       <c r="K2" s="1">
         <f t="shared" ref="K2:K19" si="0">AVERAGE(A2:J2)</f>
-        <v>93.029412399999998</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+        <v>93.417369499999992</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3">
-        <v>64.91713</v>
+        <v>98.099045000000004</v>
       </c>
       <c r="B3">
-        <v>58.694830000000003</v>
+        <v>100</v>
       </c>
       <c r="C3">
-        <v>53.138236999999997</v>
+        <v>74.857795999999993</v>
       </c>
       <c r="D3">
-        <v>81.394159999999999</v>
+        <v>98.436713999999995</v>
       </c>
       <c r="E3">
-        <v>34.964302000000004</v>
+        <v>60.684615999999998</v>
       </c>
       <c r="F3">
-        <v>81.120149999999995</v>
+        <v>88.159255999999999</v>
       </c>
       <c r="G3">
-        <v>73.232085999999995</v>
+        <v>79.897999999999996</v>
       </c>
       <c r="H3">
-        <v>41.018925000000003</v>
+        <v>95.682379999999995</v>
       </c>
       <c r="I3">
-        <v>39.097285999999997</v>
+        <v>85.65719</v>
       </c>
       <c r="J3">
-        <v>38.339134000000001</v>
+        <v>98.268839999999997</v>
       </c>
       <c r="K3" s="1">
         <f t="shared" si="0"/>
-        <v>56.591624000000003</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+        <v>87.974383700000004</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4">
-        <v>82.764560000000003</v>
+        <v>91.760050000000007</v>
       </c>
       <c r="B4">
-        <v>90.35727</v>
+        <v>81.883194000000003</v>
       </c>
       <c r="C4">
-        <v>70.561859999999996</v>
+        <v>75.33802</v>
       </c>
       <c r="D4">
-        <v>66.633960000000002</v>
+        <v>75.432900000000004</v>
       </c>
       <c r="E4">
-        <v>93.272670000000005</v>
+        <v>92.94829</v>
       </c>
       <c r="F4">
-        <v>87.862520000000004</v>
+        <v>94.474760000000003</v>
       </c>
       <c r="G4">
-        <v>84.869</v>
+        <v>98.429694999999995</v>
       </c>
       <c r="H4">
-        <v>37.139656000000002</v>
+        <v>91.08614</v>
       </c>
       <c r="I4">
-        <v>82.696820000000002</v>
+        <v>85.732010000000002</v>
       </c>
       <c r="J4">
-        <v>89.617660000000001</v>
+        <v>88.436689999999999</v>
       </c>
       <c r="K4" s="1">
         <f t="shared" si="0"/>
-        <v>78.57759759999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+        <v>87.552174899999997</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5">
-        <v>96.881799999999998</v>
+        <v>99.318436000000005</v>
       </c>
       <c r="B5">
-        <v>94.585089999999994</v>
+        <v>93.599159999999998</v>
       </c>
       <c r="C5">
-        <v>98.383539999999996</v>
+        <v>99.508895999999993</v>
       </c>
       <c r="D5">
-        <v>95.187545999999998</v>
+        <v>99.064229999999995</v>
       </c>
       <c r="E5">
-        <v>99.554564999999997</v>
+        <v>95.591179999999994</v>
       </c>
       <c r="F5">
-        <v>85.997444000000002</v>
+        <v>88.502210000000005</v>
       </c>
       <c r="G5">
-        <v>86.05247</v>
+        <v>97.16507</v>
       </c>
       <c r="H5">
-        <v>94.651650000000004</v>
+        <v>92.777780000000007</v>
       </c>
       <c r="I5">
-        <v>93.723259999999996</v>
+        <v>97.767685</v>
       </c>
       <c r="J5">
-        <v>97.777780000000007</v>
+        <v>97.410285999999999</v>
       </c>
       <c r="K5" s="1">
         <f t="shared" si="0"/>
-        <v>94.279514499999991</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+        <v>96.07049330000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6">
-        <v>39.682755</v>
+        <v>99.797470000000004</v>
       </c>
       <c r="B6">
-        <v>39.441699999999997</v>
+        <v>92.269149999999996</v>
       </c>
       <c r="C6">
-        <v>44.923960000000001</v>
+        <v>96.726119999999995</v>
       </c>
       <c r="D6">
-        <v>36.876710000000003</v>
+        <v>100</v>
       </c>
       <c r="E6">
-        <v>38.666812999999998</v>
+        <v>99.049285999999995</v>
       </c>
       <c r="F6">
-        <v>57.435524000000001</v>
+        <v>100</v>
       </c>
       <c r="G6">
-        <v>58.438366000000002</v>
+        <v>100</v>
       </c>
       <c r="H6">
-        <v>32.903399999999998</v>
+        <v>100</v>
       </c>
       <c r="I6">
-        <v>61.194262999999999</v>
+        <v>98.656679999999994</v>
       </c>
       <c r="J6">
-        <v>48.840220000000002</v>
+        <v>99.793390000000002</v>
       </c>
       <c r="K6" s="1">
         <f t="shared" si="0"/>
-        <v>45.840371099999992</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+        <v>98.62920960000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7">
-        <v>58.860152999999997</v>
+        <v>93.83887</v>
       </c>
       <c r="B7">
-        <v>59.706963000000002</v>
+        <v>98.471739999999997</v>
       </c>
       <c r="C7">
-        <v>77.061676000000006</v>
+        <v>97.036569999999998</v>
       </c>
       <c r="D7">
-        <v>67.0685</v>
+        <v>94.211579999999998</v>
       </c>
       <c r="E7">
-        <v>67.460750000000004</v>
+        <v>97.669200000000004</v>
       </c>
       <c r="F7">
-        <v>70.969695999999999</v>
+        <v>86.02852</v>
       </c>
       <c r="G7">
-        <v>56.861060000000002</v>
+        <v>100</v>
       </c>
       <c r="H7">
-        <v>46.754677000000001</v>
+        <v>94.619315999999998</v>
       </c>
       <c r="I7">
-        <v>40.609473999999999</v>
+        <v>89.819694999999996</v>
       </c>
       <c r="J7">
-        <v>60.408366999999998</v>
+        <v>94.869730000000004</v>
       </c>
       <c r="K7" s="1">
         <f t="shared" si="0"/>
-        <v>60.576131600000011</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+        <v>94.656522100000004</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8">
-        <v>77.40616</v>
+        <v>80.543499999999995</v>
       </c>
       <c r="B8">
-        <v>74.783379999999994</v>
+        <v>93.096050000000005</v>
       </c>
       <c r="C8">
-        <v>72.513724999999994</v>
+        <v>81.272480000000002</v>
       </c>
       <c r="D8">
-        <v>84.737624999999994</v>
+        <v>81.703370000000007</v>
       </c>
       <c r="E8">
-        <v>65.450860000000006</v>
+        <v>89.491164999999995</v>
       </c>
       <c r="F8">
-        <v>71.288709999999995</v>
+        <v>88.131270000000001</v>
       </c>
       <c r="G8">
-        <v>85.139595</v>
+        <v>76.253649999999993</v>
       </c>
       <c r="H8">
-        <v>78.072069999999997</v>
+        <v>98.103520000000003</v>
       </c>
       <c r="I8">
-        <v>67.378270000000001</v>
+        <v>88.588920000000002</v>
       </c>
       <c r="J8">
-        <v>76.251080000000002</v>
+        <v>86.7102</v>
       </c>
       <c r="K8" s="1">
         <f t="shared" si="0"/>
-        <v>75.302147500000018</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+        <v>86.389412500000006</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9">
-        <v>88.015339999999995</v>
+        <v>98.443950000000001</v>
       </c>
       <c r="B9">
-        <v>87.931039999999996</v>
+        <v>99.037480000000002</v>
       </c>
       <c r="C9">
-        <v>86.514719999999997</v>
+        <v>99.897720000000007</v>
       </c>
       <c r="D9">
-        <v>98.26464</v>
+        <v>99.864620000000002</v>
       </c>
       <c r="E9">
-        <v>97.848240000000004</v>
+        <v>95.889983999999998</v>
       </c>
       <c r="F9">
-        <v>81.363640000000004</v>
+        <v>99.929839999999999</v>
       </c>
       <c r="G9">
-        <v>75.729163999999997</v>
+        <v>97.776349999999994</v>
       </c>
       <c r="H9">
-        <v>63.87697</v>
+        <v>98.736046000000002</v>
       </c>
       <c r="I9">
-        <v>77.985740000000007</v>
+        <v>98.536270000000002</v>
       </c>
       <c r="J9">
-        <v>75.922809999999998</v>
+        <v>84.487465</v>
       </c>
       <c r="K9" s="1">
         <f t="shared" si="0"/>
-        <v>83.345230400000005</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+        <v>97.259972499999989</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10">
-        <v>77.344772769777407</v>
+        <v>99.681219999999996</v>
       </c>
       <c r="B10">
-        <v>75.797175986534498</v>
+        <v>98.865036000000003</v>
       </c>
       <c r="C10">
-        <v>76.323171872077793</v>
+        <v>87.969480000000004</v>
       </c>
       <c r="D10">
-        <v>72.105853749766197</v>
+        <v>97.40061</v>
       </c>
       <c r="E10">
-        <v>71.247896016457801</v>
+        <v>98.292090000000002</v>
       </c>
       <c r="F10">
-        <v>82.020291752384495</v>
+        <v>94.473579999999998</v>
       </c>
       <c r="G10">
-        <v>83.046568169066703</v>
+        <v>92.245369999999994</v>
       </c>
       <c r="H10">
-        <v>62.083878810547901</v>
+        <v>99.386690000000002</v>
       </c>
       <c r="I10">
-        <v>76.447073125116802</v>
+        <v>99.533259999999999</v>
       </c>
       <c r="J10">
-        <v>77.417243314007806</v>
+        <v>91.210380000000001</v>
       </c>
       <c r="K10" s="1">
         <f t="shared" si="0"/>
-        <v>75.383392556573739</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+        <v>95.905771600000008</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11">
-        <v>76.738715171813894</v>
+        <v>100</v>
       </c>
       <c r="B11">
-        <v>77.602916955947805</v>
+        <v>98.290595999999994</v>
       </c>
       <c r="C11">
-        <v>77.094399929046602</v>
+        <v>94.303799999999995</v>
       </c>
       <c r="D11">
-        <v>78.795903921127305</v>
+        <v>65.382225000000005</v>
       </c>
       <c r="E11">
-        <v>75.603497028350802</v>
+        <v>92.781689999999998</v>
       </c>
       <c r="F11">
-        <v>79.503607749938894</v>
+        <v>77.097009999999997</v>
       </c>
       <c r="G11">
-        <v>78.714162111282306</v>
+        <v>91.913049999999998</v>
       </c>
       <c r="H11">
-        <v>62.975013256072998</v>
+        <v>84.963620000000006</v>
       </c>
       <c r="I11">
-        <v>70.294010639190603</v>
+        <v>82.211913999999993</v>
       </c>
       <c r="J11">
-        <v>75.497651100158606</v>
+        <v>98.886830000000003</v>
       </c>
       <c r="K11" s="1">
         <f t="shared" si="0"/>
-        <v>75.281987786292973</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+        <v>88.583073499999983</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12">
-        <v>70.852684532399905</v>
+        <v>99.424385000000001</v>
       </c>
       <c r="B12">
-        <v>69.970656371112895</v>
+        <v>97.704089999999994</v>
       </c>
       <c r="C12">
-        <v>70.499030292927301</v>
+        <v>99.737260000000006</v>
       </c>
       <c r="D12">
-        <v>65.595863087811097</v>
+        <v>100</v>
       </c>
       <c r="E12">
-        <v>63.774972074662998</v>
+        <v>85.044250000000005</v>
       </c>
       <c r="F12">
-        <v>76.354593179033898</v>
+        <v>100</v>
       </c>
       <c r="G12">
-        <v>77.981995391157298</v>
+        <v>95.868589999999998</v>
       </c>
       <c r="H12">
-        <v>53.582865881859497</v>
+        <v>99.058080000000004</v>
       </c>
       <c r="I12">
-        <v>69.969290706866303</v>
+        <v>100</v>
       </c>
       <c r="J12">
-        <v>71.530112392570899</v>
+        <v>99.896050000000002</v>
       </c>
       <c r="K12" s="1">
         <f t="shared" si="0"/>
-        <v>69.011206391040204</v>
+        <v>97.673270500000015</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>99.563800000000001</v>
+      </c>
+      <c r="B13">
+        <v>98.494630000000001</v>
+      </c>
+      <c r="C13">
+        <v>97.337590000000006</v>
+      </c>
+      <c r="D13">
+        <v>87.404579999999996</v>
+      </c>
+      <c r="E13">
+        <v>97.749200000000002</v>
+      </c>
+      <c r="F13">
+        <v>91.497979999999998</v>
+      </c>
+      <c r="G13">
+        <v>96.805115000000001</v>
+      </c>
+      <c r="H13">
+        <v>99.890945000000002</v>
+      </c>
+      <c r="I13">
+        <v>87.19453</v>
+      </c>
+      <c r="J13">
+        <v>99.647480000000002</v>
+      </c>
+      <c r="K13" s="1">
+        <f t="shared" si="0"/>
+        <v>95.558584999999994</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>86.743039999999993</v>
+      </c>
+      <c r="B14">
+        <v>95.174260000000004</v>
+      </c>
+      <c r="C14">
+        <v>69.089714000000001</v>
+      </c>
+      <c r="D14">
+        <v>91.650670000000005</v>
+      </c>
+      <c r="E14">
+        <v>88.385993999999997</v>
+      </c>
+      <c r="F14">
+        <v>51.392890000000001</v>
+      </c>
+      <c r="G14">
+        <v>77.463710000000006</v>
+      </c>
+      <c r="H14">
+        <v>98.41713</v>
+      </c>
+      <c r="I14">
+        <v>63.242280000000001</v>
+      </c>
+      <c r="J14">
+        <v>77.242890000000003</v>
+      </c>
+      <c r="K14" s="1">
+        <f t="shared" si="0"/>
+        <v>79.88025780000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>72.63964</v>
+      </c>
+      <c r="B15">
+        <v>68.607370000000003</v>
+      </c>
+      <c r="C15">
+        <v>71.331764000000007</v>
+      </c>
+      <c r="D15">
+        <v>65.450355999999999</v>
+      </c>
+      <c r="E15">
+        <v>61.176913999999996</v>
+      </c>
+      <c r="F15">
+        <v>54.978349999999999</v>
+      </c>
+      <c r="G15">
+        <v>64.059970000000007</v>
+      </c>
+      <c r="H15">
+        <v>63.287210000000002</v>
+      </c>
+      <c r="I15">
+        <v>81.664824999999993</v>
+      </c>
+      <c r="J15">
+        <v>74.836020000000005</v>
+      </c>
+      <c r="K15" s="1">
+        <f t="shared" si="0"/>
+        <v>67.803241899999989</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>100</v>
+      </c>
+      <c r="B16">
+        <v>49.952759999999998</v>
+      </c>
+      <c r="C16">
+        <v>72.08081</v>
+      </c>
+      <c r="D16">
+        <v>86.66301</v>
+      </c>
+      <c r="E16">
+        <v>94.965810000000005</v>
+      </c>
+      <c r="F16">
+        <v>90.846050000000005</v>
+      </c>
+      <c r="G16">
+        <v>93.845344999999995</v>
+      </c>
+      <c r="H16">
+        <v>89.5</v>
+      </c>
+      <c r="I16">
+        <v>78.672989999999999</v>
+      </c>
+      <c r="J16">
+        <v>93.087249999999997</v>
+      </c>
+      <c r="K16" s="1">
+        <f t="shared" si="0"/>
+        <v>84.961402499999991</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>88.647490254761706</v>
+      </c>
+      <c r="B17">
+        <v>87.8808032662713</v>
+      </c>
+      <c r="C17">
+        <v>86.639324576474706</v>
+      </c>
+      <c r="D17">
+        <v>86.585748859206703</v>
+      </c>
+      <c r="E17">
+        <v>85.621385948382496</v>
+      </c>
+      <c r="F17">
+        <v>82.384673649984293</v>
+      </c>
+      <c r="G17">
+        <v>86.672578469951404</v>
+      </c>
+      <c r="H17">
+        <v>89.988730624988406</v>
+      </c>
+      <c r="I17">
+        <v>89.135214025753299</v>
+      </c>
+      <c r="J17">
+        <v>88.835928984462996</v>
+      </c>
+      <c r="K17" s="1">
+        <f t="shared" si="0"/>
+        <v>87.239187866023727</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>91.851609945297199</v>
+      </c>
+      <c r="B18">
+        <v>90.336132049560504</v>
+      </c>
+      <c r="C18">
+        <v>88.008213043212805</v>
+      </c>
+      <c r="D18">
+        <v>88.329350948333698</v>
+      </c>
+      <c r="E18">
+        <v>89.815318584442096</v>
+      </c>
+      <c r="F18">
+        <v>86.456423997879</v>
+      </c>
+      <c r="G18">
+        <v>90.686655044555593</v>
+      </c>
+      <c r="H18">
+        <v>94.038152694702106</v>
+      </c>
+      <c r="I18">
+        <v>88.091897964477496</v>
+      </c>
+      <c r="J18">
+        <v>91.909420490264793</v>
+      </c>
+      <c r="K18" s="1">
+        <f t="shared" si="0"/>
+        <v>89.952317476272526</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>87.3622692078971</v>
+      </c>
+      <c r="B19">
+        <v>86.626402722459503</v>
+      </c>
+      <c r="C19">
+        <v>85.177477955344699</v>
+      </c>
+      <c r="D19">
+        <v>85.141995010530593</v>
+      </c>
+      <c r="E19">
+        <v>84.095766866740504</v>
+      </c>
+      <c r="F19">
+        <v>80.582646055009306</v>
+      </c>
+      <c r="G19">
+        <v>85.190171299562707</v>
+      </c>
+      <c r="H19">
+        <v>88.931814027006197</v>
+      </c>
+      <c r="I19">
+        <v>87.932867444048398</v>
+      </c>
+      <c r="J19">
+        <v>87.596572229939596</v>
+      </c>
+      <c r="K19" s="1">
+        <f t="shared" si="0"/>
+        <v>85.863798281853875</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48B3FC5D-CBEF-4852-9492-3A8AFB021ED5}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2199,8 +2199,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0042C639-A362-44FB-9C81-3BA17FB792FE}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>